--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104710_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104710_W28.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2647</v>
+        <v>6.9429</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1738</v>
+        <v>8.077199999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9091</v>
+        <v>-1.1343</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1979</v>
+        <v>6.1825</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4214</v>
+        <v>1.4162</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7765</v>
+        <v>4.7663</v>
       </c>
       <c r="J2" t="n">
-        <v>7.2386</v>
+        <v>7.2032</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2484</v>
+        <v>3.2265</v>
       </c>
       <c r="L2" t="n">
-        <v>3.9902</v>
+        <v>3.9767</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0407</v>
+        <v>-1.0207</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.827</v>
+        <v>-1.8103</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.199</v>
+        <v>-0.0999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1089</v>
+        <v>0.0624</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0901</v>
+        <v>-0.1623</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4397</v>
+        <v>1.3875</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5679</v>
+        <v>-0.2429</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0077</v>
+        <v>1.6304</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5004</v>
+        <v>2.4848</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0736</v>
+        <v>3.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5732</v>
+        <v>-0.5829</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9525</v>
+        <v>2.9118</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0753</v>
+        <v>3.0542</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1228</v>
+        <v>-0.1424</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4521</v>
+        <v>-0.427</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3802</v>
+        <v>-0.4144</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2521</v>
+        <v>-0.8784</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8719</v>
+        <v>0.4639</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3541</v>
+        <v>0.1785</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3283</v>
+        <v>0.3818</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9742</v>
+        <v>-0.2032</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5953000000000001</v>
+        <v>0.7358</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3016</v>
+        <v>-0.1207</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7063</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5441</v>
+        <v>0.5631</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4126</v>
+        <v>0.4392</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1393</v>
+        <v>0.1727</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.433</v>
+        <v>-0.2446</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7063</v>
+        <v>0.4173</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7226</v>
+        <v>0.2347</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8257</v>
+        <v>-0.1813</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1031</v>
+        <v>0.416</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1236</v>
+        <v>0.0528</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1592</v>
+        <v>1.9716</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0355</v>
+        <v>-1.9188</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7371</v>
+        <v>-0.5985</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1212</v>
+        <v>-1.2984</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8583</v>
+        <v>0.6998</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5765</v>
+        <v>1.5236</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4451</v>
+        <v>1.3997</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1605</v>
+        <v>-2.1221</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2526</v>
+        <v>-1.4223</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4132</v>
+        <v>-0.6998</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1863</v>
+        <v>0.4237</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4174</v>
+        <v>0.4967</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6037</v>
+        <v>-0.073</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2534</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8853</v>
+        <v>-0.5752</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.3011</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8032</v>
+        <v>-0.8764</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1211</v>
+        <v>-0.724</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0202</v>
+        <v>-2.9466</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1413</v>
+        <v>2.2226</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1266</v>
+        <v>0.4097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.052</v>
+        <v>-1.4521</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>1.8618</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2477</v>
+        <v>-1.1337</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0318</v>
+        <v>-1.4945</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2159</v>
+        <v>0.3608</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1252</v>
+        <v>-0.9211</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2087</v>
+        <v>-0.8111</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0835</v>
+        <v>-0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>0.387</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0861</v>
+        <v>-0.7513</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0226</v>
+        <v>-0.0829</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0635</v>
+        <v>-0.6684</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7232</v>
+        <v>-0.1171</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9436</v>
+        <v>0.0228</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2204</v>
+        <v>-0.14</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4348</v>
+        <v>0.1262</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4311</v>
+        <v>0.0517</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8658</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1579</v>
+        <v>-0.2433</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5125</v>
+        <v>-0.0289</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3546</v>
+        <v>-0.2144</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.429</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1644</v>
+        <v>-0.2091</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2646</v>
+        <v>0.2091</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9884</v>
+        <v>-2.227</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1519</v>
+        <v>-1.8049</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8365</v>
+        <v>-0.4221</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7499</v>
+        <v>-0.7695</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9019</v>
+        <v>1.0911</v>
       </c>
       <c r="I8" t="n">
-        <v>0.152</v>
+        <v>-1.8605</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4858</v>
+        <v>0.2603</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3739</v>
+        <v>1.2066</v>
       </c>
       <c r="L8" t="n">
-        <v>0.112</v>
+        <v>-0.9463</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2357</v>
+        <v>-1.0298</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2758</v>
+        <v>-0.1155</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04</v>
+        <v>-0.9143</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1724</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1179</v>
+        <v>-0.9271</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0544</v>
+        <v>0.1524</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5651</v>
+        <v>-2.2701</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9037</v>
+        <v>-1.4503</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6613</v>
+        <v>-0.8197</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7755</v>
+        <v>-0.7425</v>
       </c>
       <c r="H9" t="n">
-        <v>1.085</v>
+        <v>-0.8991</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8605</v>
+        <v>0.1566</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2738</v>
+        <v>0.4769</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2122</v>
+        <v>0.3652</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9383</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0494</v>
+        <v>-1.2194</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1272</v>
+        <v>-1.2643</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9222</v>
+        <v>0.0449</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1091</v>
+        <v>-0.4577</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0434</v>
+        <v>-0.4021</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0556</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2231</v>
+        <v>-3.5579</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0604</v>
+        <v>-2.6007</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1627</v>
+        <v>-0.9573</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.4326</v>
+        <v>-4.439</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9883</v>
+        <v>-1.993</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4443</v>
+        <v>-2.446</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.6396</v>
+        <v>-2.6616</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2162</v>
+        <v>-1.2313</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.793</v>
+        <v>-1.7774</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4609</v>
+        <v>0.1299</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9648</v>
+        <v>0.448</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5039</v>
+        <v>-0.3181</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4883</v>
+        <v>-5.4861</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0712</v>
+        <v>-1.0328</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4171</v>
+        <v>-4.4533</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6616</v>
+        <v>-2.6623</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9467</v>
+        <v>-2.9359</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2851</v>
+        <v>0.2736</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6186</v>
+        <v>-0.6375</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0429</v>
+        <v>-2.0248</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2989</v>
+        <v>-2.2841</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5854</v>
+        <v>0.5827</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6816</v>
+        <v>0.7428</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.1601</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4731</v>
+        <v>-5.6131</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7516</v>
+        <v>-1.9276</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7215</v>
+        <v>-3.6855</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5625</v>
+        <v>-2.5632</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5873</v>
+        <v>-0.5833</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9752</v>
+        <v>-1.9799</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.8728</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2007</v>
+        <v>0.1929</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.053</v>
+        <v>-1.0656</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7103</v>
+        <v>-1.6904</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6986</v>
+        <v>0.1487</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7652</v>
+        <v>0.0834</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0665</v>
+        <v>0.0653</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.6445</v>
+        <v>-6.5754</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.2915</v>
+        <v>-5.438</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.353</v>
+        <v>-1.1375</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.768</v>
+        <v>-5.7761</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.2841</v>
+        <v>-2.2888</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.4839</v>
+        <v>-3.4873</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.1355</v>
+        <v>-4.1715</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1021</v>
+        <v>-1.1246</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.0335</v>
+        <v>-3.0469</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6325</v>
+        <v>-1.6047</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1821</v>
+        <v>-1.1642</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5836</v>
+        <v>-0.5018</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1825</v>
+        <v>-0.2861</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4011</v>
+        <v>-0.2157</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.1718</v>
+        <v>-18.4944</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.2416</v>
+        <v>-3.8484</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.9299</v>
+        <v>-14.6461</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.9543</v>
+        <v>-8.989099999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.474499999999999</v>
+        <v>-7.468000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4798</v>
+        <v>-1.521299999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>5.386699999999999</v>
+        <v>5.131400000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>4.028100000000001</v>
+        <v>3.885199999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3585</v>
+        <v>1.246300000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.341</v>
+        <v>-14.1206</v>
       </c>
       <c r="N14" t="n">
-        <v>-11.5027</v>
+        <v>-11.353</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.8382</v>
+        <v>-2.7676</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.665334536937735e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2077</v>
+        <v>-10.2437</v>
       </c>
       <c r="R14" t="n">
-        <v>10.2077</v>
+        <v>10.2437</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3439</v>
+        <v>-1.6499</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.570600000000001</v>
+        <v>-1.8619</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2268000000000002</v>
+        <v>0.2119</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.8736</v>
+        <v>-7.855499999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>3.149699999999999</v>
+        <v>3.1255</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.0233</v>
+        <v>-10.9811</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. TAVARES</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.880100000000001</v>
+        <v>7.1939</v>
       </c>
       <c r="E15" t="n">
-        <v>6.9181</v>
+        <v>3.8898</v>
       </c>
       <c r="F15" t="n">
-        <v>1.962</v>
+        <v>3.3042</v>
       </c>
       <c r="G15" t="n">
-        <v>5.94</v>
+        <v>2.1113</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4761</v>
+        <v>1.4796</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4639</v>
+        <v>0.6317</v>
       </c>
       <c r="J15" t="n">
-        <v>5.2084</v>
+        <v>0.7577</v>
       </c>
       <c r="K15" t="n">
-        <v>5.0219</v>
+        <v>0.4752</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1866</v>
+        <v>0.2826</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7316</v>
+        <v>1.3536</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4542</v>
+        <v>1.0044</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2773</v>
+        <v>0.3492</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4884</v>
+        <v>1.3393</v>
       </c>
       <c r="T15" t="n">
-        <v>1.978</v>
+        <v>0.5269</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5104</v>
+        <v>0.8124</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3214</v>
+        <v>3.9709</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>3.9709</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>E. TAVARES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.3749</v>
+        <v>7.0869</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8207</v>
+        <v>5.8303</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5543</v>
+        <v>1.2566</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1169</v>
+        <v>5.9504</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4878</v>
+        <v>5.4716</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6291</v>
+        <v>0.4788</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7913</v>
+        <v>5.1849</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4982</v>
+        <v>4.9987</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2931</v>
+        <v>0.1862</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3256</v>
+        <v>0.7655</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9896</v>
+        <v>0.4729</v>
       </c>
       <c r="O16" t="n">
-        <v>0.336</v>
+        <v>0.2926</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4998</v>
+        <v>1.6797</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4053</v>
+        <v>0.9217</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0945</v>
+        <v>0.758</v>
       </c>
       <c r="V16" t="n">
-        <v>3.9851</v>
+        <v>-0.3155</v>
       </c>
       <c r="W16" t="n">
-        <v>3.9851</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3636</v>
+        <v>3.4131</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0017</v>
+        <v>-0.0132</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3653</v>
+        <v>3.4263</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6177</v>
+        <v>0.6264</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2295</v>
+        <v>-1.2238</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8472</v>
+        <v>1.8502</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3374</v>
+        <v>-0.352</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.4169</v>
+        <v>-1.4242</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9784</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8405</v>
+        <v>0.8746</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3357</v>
+        <v>0.3388</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5048</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5373</v>
+        <v>1.7969</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3275</v>
+        <v>0.4899</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7903</v>
+        <v>1.307</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1241</v>
+        <v>1.6006</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0939</v>
+        <v>-0.0289</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9698</v>
+        <v>1.6294</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1225</v>
+        <v>1.7421</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5833</v>
+        <v>0.4169</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4608</v>
+        <v>1.3252</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9984</v>
+        <v>-0.1416</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4894</v>
+        <v>-0.4458</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.509</v>
+        <v>0.3043</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3451</v>
+        <v>0.6516</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0484</v>
+        <v>0.1136</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3935</v>
+        <v>0.538</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.225</v>
+        <v>1.5064</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1609</v>
+        <v>3.0636</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0641</v>
+        <v>-1.5572</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6021</v>
+        <v>-0.59</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0318</v>
+        <v>1.6147</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6339</v>
+        <v>-2.2046</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7638</v>
+        <v>1.4147</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4258</v>
+        <v>2.592</v>
       </c>
       <c r="L19" t="n">
-        <v>1.338</v>
+        <v>-1.1773</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1617</v>
+        <v>-2.0047</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4576</v>
+        <v>-0.9774</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2959</v>
+        <v>-1.0273</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0765</v>
+        <v>-0.3785</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2419</v>
+        <v>-0.4601</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3185</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1033</v>
+        <v>1.4224</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8384</v>
+        <v>2.0535</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7351</v>
+        <v>-0.6312</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.839</v>
+        <v>0.1183</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.306</v>
+        <v>2.0829</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.533</v>
+        <v>-1.9646</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5639</v>
+        <v>1.09</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4892</v>
+        <v>2.5576</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>-1.4676</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4029</v>
+        <v>-0.9717</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7953</v>
+        <v>-0.4747</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6077</v>
+        <v>-0.497</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2184</v>
+        <v>0.2358</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0212</v>
+        <v>-0.2837</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2395</v>
+        <v>0.5195</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2534</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0684</v>
+        <v>0.8632</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8766</v>
+        <v>2.3532</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8082</v>
+        <v>-1.4901</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5795</v>
+        <v>-0.823</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6249</v>
+        <v>-0.2991</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2044</v>
+        <v>-0.5239</v>
       </c>
       <c r="J21" t="n">
-        <v>1.453</v>
+        <v>1.5568</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6179</v>
+        <v>1.4824</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1649</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0325</v>
+        <v>-2.3799</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.993</v>
+        <v>-1.7814</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0395</v>
+        <v>-0.5984</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8323</v>
+        <v>-0.4716</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6956</v>
+        <v>-0.4509</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1367</v>
+        <v>-0.0207</v>
       </c>
       <c r="V21" t="n">
-        <v>1.7997</v>
+        <v>1.2472</v>
       </c>
       <c r="W21" t="n">
-        <v>2.3461</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3597</v>
+        <v>0.8174</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2146</v>
+        <v>1.7652</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5743</v>
+        <v>-0.9478</v>
       </c>
       <c r="G22" t="n">
-        <v>4.7506</v>
+        <v>4.7498</v>
       </c>
       <c r="H22" t="n">
-        <v>3.3245</v>
+        <v>3.3258</v>
       </c>
       <c r="I22" t="n">
-        <v>1.426</v>
+        <v>1.424</v>
       </c>
       <c r="J22" t="n">
-        <v>5.104</v>
+        <v>5.0753</v>
       </c>
       <c r="K22" t="n">
-        <v>3.169</v>
+        <v>3.1543</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9351</v>
+        <v>1.921</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3534</v>
+        <v>-0.3255</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0688</v>
+        <v>0.1163</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2601</v>
+        <v>0.3319</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8087</v>
+        <v>-0.2157</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9553</v>
+        <v>-0.7226</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4457</v>
+        <v>0.6415</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1811</v>
+        <v>-0.1764</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6478</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.829</v>
+        <v>-0.8282</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6771</v>
+        <v>-0.6807</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4959</v>
+        <v>0.5043</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6132</v>
+        <v>0.6173</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7821</v>
+        <v>-0.36</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2782</v>
+        <v>-0.0419</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5039</v>
+        <v>-0.3181</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.1324</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2512</v>
+        <v>-1.1379</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1188</v>
+        <v>0.2977</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6718</v>
+        <v>-1.6616</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7865</v>
+        <v>-1.781</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1147</v>
+        <v>0.1194</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6251</v>
+        <v>-0.629</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0467</v>
+        <v>-1.0326</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O24" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5928</v>
+        <v>-0.3183</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6261</v>
+        <v>-0.5089</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0333</v>
+        <v>0.1906</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="25">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.6461</v>
+        <v>-1.3698</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7627</v>
+        <v>-1.6654</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1165</v>
+        <v>0.2957</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.1808</v>
+        <v>-2.1747</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.6709</v>
+        <v>-3.6705</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4901</v>
+        <v>1.4958</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0437</v>
+        <v>-1.0567</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.2379</v>
+        <v>-2.2483</v>
       </c>
       <c r="L25" t="n">
-        <v>1.1941</v>
+        <v>1.1916</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.1371</v>
+        <v>-1.118</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.433</v>
+        <v>-1.4223</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.2845</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6775</v>
+        <v>-0.5601</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1195</v>
+        <v>0.2755</v>
       </c>
       <c r="V25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,58 +2437,58 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.733</v>
+        <v>-1.8278</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.256</v>
+        <v>-1.2603</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.477</v>
+        <v>-0.5675</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7449</v>
+        <v>-0.7419</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1559</v>
+        <v>-0.1551</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.7622</v>
+        <v>-0.7592</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1461</v>
+        <v>0.0523</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2852</v>
+        <v>0.1917</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>19.1718</v>
+        <v>19.9812</v>
       </c>
       <c r="E27" t="n">
-        <v>14.9299</v>
+        <v>14.6461</v>
       </c>
       <c r="F27" t="n">
-        <v>4.2418</v>
+        <v>5.3352</v>
       </c>
       <c r="G27" t="n">
-        <v>8.954300000000002</v>
+        <v>8.989200000000002</v>
       </c>
       <c r="H27" t="n">
-        <v>7.4744</v>
+        <v>7.467899999999998</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4796</v>
+        <v>1.5212</v>
       </c>
       <c r="J27" t="n">
-        <v>14.3409</v>
+        <v>14.1203</v>
       </c>
       <c r="K27" t="n">
-        <v>11.5026</v>
+        <v>11.3528</v>
       </c>
       <c r="L27" t="n">
-        <v>2.8382</v>
+        <v>2.7677</v>
       </c>
       <c r="M27" t="n">
-        <v>-5.386699999999999</v>
+        <v>-5.1314</v>
       </c>
       <c r="N27" t="n">
-        <v>-4.0282</v>
+        <v>-3.8851</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.3586</v>
+        <v>-1.2462</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="Q27" t="n">
-        <v>-10.2075</v>
+        <v>-10.2435</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S27" t="n">
-        <v>2.344</v>
+        <v>3.1367</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2266999999999998</v>
+        <v>-0.2121000000000003</v>
       </c>
       <c r="U27" t="n">
-        <v>2.5709</v>
+        <v>3.3486</v>
       </c>
       <c r="V27" t="n">
-        <v>7.8736</v>
+        <v>7.855499999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>11.0234</v>
+        <v>10.981</v>
       </c>
       <c r="X27" t="n">
-        <v>-3.1497</v>
+        <v>-3.1256</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104710_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104710_W28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-10.9811</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104710_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-3.1256</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
